--- a/Output/Hourly Scan_14 Jul 2026.xlsx
+++ b/Output/Hourly Scan_14 Jul 2026.xlsx
@@ -509,7 +509,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>40.51</v>
+        <v>47.92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>54.86</v>
+        <v>41.11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>44.92</v>
+        <v>43.32</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>45.07</v>
+        <v>57.93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>64.43000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>52.79</v>
+        <v>45.23</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -701,11 +701,11 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>54.92</v>
+        <v>63.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -733,7 +733,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>42.34</v>
+        <v>43.06</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -765,11 +765,11 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>64.56999999999999</v>
+        <v>55.56</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -797,7 +797,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>52.03</v>
+        <v>52.62</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -829,11 +829,11 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>62.53</v>
+        <v>49.75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -861,11 +861,11 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>50.44</v>
+        <v>38.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -893,11 +893,11 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>51.72</v>
+        <v>36.28</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -925,7 +925,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>49.38</v>
+        <v>42.51</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>38.77</v>
+        <v>31.49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -989,11 +989,11 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>76.20999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1021,11 +1021,11 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>65.14</v>
+        <v>44.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>59.22</v>
+        <v>47.76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>40.28</v>
+        <v>31.36</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1117,11 +1117,11 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>72.28</v>
+        <v>43.91</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1149,11 +1149,11 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>49.13</v>
+        <v>37.35</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>39.13</v>
+        <v>37.08</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>49.37</v>
+        <v>50.37</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>58.99</v>
+        <v>56.97</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>45.71</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1309,11 +1309,11 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>53.24</v>
+        <v>72.47</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>54.85</v>
+        <v>46.91</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>44.55</v>
+        <v>48.16</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>44.66</v>
+        <v>45.13</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>36.94</v>
+        <v>22.91</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>71.13</v>
+        <v>68.28</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>62.13</v>
+        <v>43.92</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>52.87</v>
+        <v>48.41</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>47.94</v>
+        <v>47.01</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>38.71</v>
+        <v>35.8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1629,11 +1629,11 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>45.59</v>
+        <v>39.52</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>50.25</v>
+        <v>49.68</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>52.45</v>
+        <v>42.09</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1725,11 +1725,11 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>43.87</v>
+        <v>39.39</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>55.4</v>
+        <v>40.57</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1789,11 +1789,11 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>52.74</v>
+        <v>38.58</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>47.84</v>
+        <v>56.27</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>75.84999999999999</v>
+        <v>47.52</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>33.9</v>
+        <v>25.86</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1949,11 +1949,11 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>48.39</v>
+        <v>37.96</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>58.27</v>
+        <v>54.18</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2013,11 +2013,11 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>44.03</v>
+        <v>30.95</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>37.97</v>
+        <v>33.06</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>42.07</v>
+        <v>48.17</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>53.15</v>
+        <v>58.76</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>55.95</v>
+        <v>45.21</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2173,11 +2173,11 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>50.54</v>
+        <v>35.98</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>72.83</v>
+        <v>74.73</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>48.41</v>
+        <v>41.07</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2269,11 +2269,11 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>43.57</v>
+        <v>37.22</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2301,11 +2301,11 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>44.81</v>
+        <v>32.64</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2333,11 +2333,11 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>57.35</v>
+        <v>39.86</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -2365,11 +2365,11 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>53.24</v>
+        <v>33.64</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -2397,11 +2397,11 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>40.16</v>
+        <v>26.77</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>54.12</v>
+        <v>44.13</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2461,11 +2461,11 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>64.25</v>
+        <v>52.37</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -2493,11 +2493,11 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>53.5</v>
+        <v>65.44</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>42.25</v>
+        <v>49.98</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2557,11 +2557,11 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>64.67</v>
+        <v>56.28</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -2589,11 +2589,11 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>37.78</v>
+        <v>63.53</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>79.56</v>
+        <v>70.77</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>68.47</v>
+        <v>55.14</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -2685,11 +2685,11 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>63.12</v>
+        <v>38.19</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>58.24</v>
+        <v>54.38</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>50.26</v>
+        <v>49.42</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>59.98</v>
+        <v>53.31</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2813,11 +2813,11 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>65.54000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -2845,7 +2845,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>49.28</v>
+        <v>42.46</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>60.78</v>
+        <v>54.3</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -2909,11 +2909,11 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>67.41</v>
+        <v>47.81</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>39.37</v>
+        <v>36.29</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2973,11 +2973,11 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>42.21</v>
+        <v>36.74</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>80.29000000000001</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>46.89</v>
+        <v>55.24</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>55.05</v>
+        <v>43.91</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3101,11 +3101,11 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>41.05</v>
+        <v>36.69</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3133,11 +3133,11 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>63.9</v>
+        <v>48.47</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>53.92</v>
+        <v>41.12</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3197,11 +3197,11 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>47.45</v>
+        <v>32.46</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>26.07</v>
+        <v>37.61</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3261,11 +3261,11 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>45.38</v>
+        <v>63.87</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>49.9</v>
+        <v>56.91</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>37.77</v>
+        <v>30.01</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>70.43000000000001</v>
+        <v>84.69</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3389,11 +3389,11 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>47.42</v>
+        <v>39.6</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>49.51</v>
+        <v>46.44</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>28.8</v>
+        <v>27.75</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3485,11 +3485,11 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>70.91</v>
+        <v>55.63</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -3517,11 +3517,11 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>58.86</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>47.07</v>
+        <v>44.37</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>59.02</v>
+        <v>42.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>56.16</v>
+        <v>52.76</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>64.72</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>56.02</v>
+        <v>48.68</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3709,11 +3709,11 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>69.02</v>
+        <v>54.85</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -3741,11 +3741,11 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>56.99</v>
+        <v>39.08</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>48.67</v>
+        <v>42.18</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>42.73</v>
+        <v>45.01</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>55.26</v>
+        <v>47.17</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>83.17</v>
+        <v>64</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>56.63</v>
+        <v>55.86</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>65.73999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>44.73</v>
+        <v>51.51</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3997,11 +3997,11 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>47.95</v>
+        <v>60.65</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>53.3</v>
+        <v>40.21</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4061,11 +4061,11 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>44.92</v>
+        <v>31.83</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>40.29</v>
+        <v>53.9</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4125,11 +4125,11 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>65.7</v>
+        <v>51.5</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -4157,11 +4157,11 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>65.29000000000001</v>
+        <v>54.15</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -4189,11 +4189,11 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>41.14</v>
+        <v>38.9</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -4221,7 +4221,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>37.99</v>
+        <v>27.63</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4253,11 +4253,11 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>54.49</v>
+        <v>33.52</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -4285,11 +4285,11 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>31.9</v>
+        <v>43.63</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>51.99</v>
+        <v>44.07</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>59.21</v>
+        <v>40.17</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>51.07</v>
+        <v>41.43</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>54.63</v>
+        <v>40.53</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4445,11 +4445,11 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>44.58</v>
+        <v>33.66</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -4477,11 +4477,11 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>55.94</v>
+        <v>62.81</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -4509,11 +4509,11 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>35.14</v>
+        <v>42.35</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -4541,11 +4541,11 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>40.14</v>
+        <v>33.46</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -4573,11 +4573,11 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>56.3</v>
+        <v>39.57</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>45.05</v>
+        <v>46.39</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>60.75</v>
+        <v>51.14</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -4669,11 +4669,11 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>39.95</v>
+        <v>49.61</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>54.84</v>
+        <v>50.81</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>42.03</v>
+        <v>52.12</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4765,11 +4765,11 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>50.82</v>
+        <v>35.48</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -4797,11 +4797,11 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>43.76</v>
+        <v>25.65</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>42.3</v>
+        <v>40.65</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>61.83</v>
+        <v>61.6</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4893,11 +4893,11 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>72.68000000000001</v>
+        <v>55.21</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>59.38</v>
+        <v>46.12</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>68.09</v>
+        <v>62.61</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>48.31</v>
+        <v>59.92</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5021,11 +5021,11 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>61.92</v>
+        <v>45.97</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -5053,7 +5053,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>72.81999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5085,11 +5085,11 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>67.97</v>
+        <v>58.61</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -5117,11 +5117,11 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>61.63</v>
+        <v>37.92</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>58.98</v>
+        <v>40.45</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5181,11 +5181,11 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>59.67</v>
+        <v>62.09</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -5213,11 +5213,11 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>39.8</v>
+        <v>51.92</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>36.21</v>
+        <v>35.78</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>49.05</v>
+        <v>57.79</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5309,11 +5309,11 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>50.51</v>
+        <v>38.24</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -5341,11 +5341,11 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>53.51</v>
+        <v>65.31</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -5373,7 +5373,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>45.4</v>
+        <v>51.7</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>44.77</v>
+        <v>53.9</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>42.17</v>
+        <v>51.09</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5469,11 +5469,11 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>65.78</v>
+        <v>49.25</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>47.53</v>
+        <v>52.2</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>39.57</v>
+        <v>36.89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>42.12</v>
+        <v>54.53</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5597,11 +5597,11 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>63.29</v>
+        <v>44.96</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -5629,11 +5629,11 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>38.41</v>
+        <v>47.48</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>37.78</v>
+        <v>37.66</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5693,11 +5693,11 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>57.48</v>
+        <v>38.43</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -5725,11 +5725,11 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>60.63</v>
+        <v>48.82</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -5757,11 +5757,11 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>61.2</v>
+        <v>51.6</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -5789,11 +5789,11 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>71.31999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -5821,11 +5821,11 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
-        <v>74.39</v>
+        <v>47.25</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>43.32</v>
+        <v>47.5</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>53.48</v>
+        <v>43.44</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5917,11 +5917,11 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>63.33</v>
+        <v>58.81</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -5949,7 +5949,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>47.34</v>
+        <v>53.27</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5981,11 +5981,11 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>43.52</v>
+        <v>35.69</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -6013,7 +6013,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>78.98999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>34.34</v>
+        <v>30.08</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>48.45</v>
+        <v>49.19</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6109,11 +6109,11 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>71.86</v>
+        <v>46.15</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -6141,11 +6141,11 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>65.86</v>
+        <v>58.37</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -6173,7 +6173,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>48.08</v>
+        <v>46.16</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6205,11 +6205,11 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>40.48</v>
+        <v>32.95</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -6237,11 +6237,11 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>65.65000000000001</v>
+        <v>46.15</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>50</v>
+        <v>47.22</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>59.22</v>
+        <v>44.5</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>48.3</v>
+        <v>45.88</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>47.13</v>
+        <v>47.11</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>49.52</v>
+        <v>47.57</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -6429,11 +6429,11 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>63.13</v>
+        <v>41.8</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -6461,7 +6461,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>52.51</v>
+        <v>47.98</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6493,11 +6493,11 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>54.41</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -6525,11 +6525,11 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>68.28</v>
+        <v>52.31</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>48.85</v>
+        <v>42.08</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>52.44</v>
+        <v>41.78</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>55.42</v>
+        <v>51.83</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>33.93</v>
+        <v>33.97</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -6685,11 +6685,11 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>41.16</v>
+        <v>39.71</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -6717,11 +6717,11 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>63.74</v>
+        <v>50.28</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -6749,7 +6749,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="n">
-        <v>48.7</v>
+        <v>52.17</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>37.46</v>
+        <v>29.43</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>49.71</v>
+        <v>45.11</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>43.29</v>
+        <v>51.18</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>55.4</v>
+        <v>52.31</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6909,11 +6909,11 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>64.09</v>
+        <v>39</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -6941,7 +6941,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>55.49</v>
+        <v>49.68</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6973,11 +6973,11 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>55.91</v>
+        <v>38.91</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -7005,11 +7005,11 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>60.16</v>
+        <v>45.47</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -7037,11 +7037,11 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>65.97</v>
+        <v>55.96</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -7069,11 +7069,11 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>57.59</v>
+        <v>34.78</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -7101,11 +7101,11 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>61.19</v>
+        <v>46.43</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>59.87</v>
+        <v>46.53</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>36.05</v>
+        <v>37.55</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -7197,11 +7197,11 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>51.42</v>
+        <v>39.61</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -7229,11 +7229,11 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>56.51</v>
+        <v>37.6</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -7261,7 +7261,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>44.67</v>
+        <v>40.43</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>53.63</v>
+        <v>44.16</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>43.88</v>
+        <v>59.46</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>50.24</v>
+        <v>50.09</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>42.53</v>
+        <v>51.57</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -7702,7 +7702,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -7728,11 +7732,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -7810,11 +7810,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -8334,7 +8330,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -8360,7 +8360,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -8676,11 +8680,7 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -8784,7 +8784,11 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -9304,7 +9308,11 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -9330,7 +9338,11 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -9382,7 +9394,11 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -9850,11 +9866,7 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -10114,7 +10126,11 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -10192,7 +10208,11 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
@@ -10452,7 +10472,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -10478,7 +10502,11 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
@@ -10660,11 +10688,7 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
@@ -10820,11 +10844,7 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
@@ -10902,7 +10922,11 @@
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
@@ -10928,7 +10952,11 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
@@ -11110,7 +11138,11 @@
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
@@ -11344,7 +11376,11 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
@@ -11422,11 +11458,7 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -11582,7 +11614,11 @@
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
@@ -11790,7 +11826,11 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -11816,7 +11856,11 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
@@ -12050,7 +12094,11 @@
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
@@ -12180,7 +12228,11 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
@@ -12310,7 +12362,11 @@
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
@@ -12598,7 +12654,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bearish EMA Pullback</t>
+          <t>Bullish EMA Pullback</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -12652,11 +12708,7 @@
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -12708,7 +12760,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -12760,11 +12816,7 @@
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
@@ -13256,7 +13308,11 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -13308,7 +13364,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -13364,7 +13424,11 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -13390,7 +13454,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -13416,11 +13484,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -13446,11 +13510,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -13476,7 +13536,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -13502,11 +13566,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -13560,7 +13620,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -13588,7 +13648,11 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -13644,11 +13708,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -13674,11 +13734,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -13704,11 +13760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -13760,11 +13812,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -13790,7 +13838,11 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -13816,11 +13868,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -13872,11 +13920,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -13902,11 +13946,7 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -13932,7 +13972,11 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -13958,7 +14002,11 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -14036,7 +14084,11 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -14170,7 +14222,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -14222,7 +14278,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -14248,7 +14308,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -14274,7 +14338,11 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -14300,7 +14368,11 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -14326,7 +14398,11 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -14352,11 +14428,7 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -14382,11 +14454,7 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -14412,7 +14480,11 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -14468,7 +14540,11 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -14494,11 +14570,7 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -14524,7 +14596,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -14550,7 +14626,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -14576,11 +14656,7 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -14606,7 +14682,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -14632,11 +14712,7 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -14662,7 +14738,11 @@
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -14688,11 +14768,7 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -14718,7 +14794,11 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -14774,7 +14854,11 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -14800,11 +14884,7 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -14830,7 +14910,11 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -14886,7 +14970,11 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -14912,11 +15000,7 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -14972,11 +15056,7 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -15030,7 +15110,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bearish Confluence</t>
+          <t>Bullish Confluence</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -15058,11 +15138,7 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
@@ -15088,11 +15164,7 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -15118,7 +15190,11 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -15144,11 +15220,7 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -15174,7 +15246,11 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -15230,11 +15306,7 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -15316,11 +15388,7 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
@@ -15464,7 +15532,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -15492,11 +15560,7 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
@@ -15522,11 +15586,7 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -15552,11 +15612,7 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -15638,7 +15694,11 @@
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -15690,7 +15750,11 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
@@ -15746,7 +15810,11 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -15828,11 +15896,7 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
@@ -15858,7 +15922,11 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -15916,7 +15984,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -16030,11 +16098,7 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -16062,7 +16126,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -16090,7 +16154,11 @@
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
@@ -16172,11 +16240,7 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
@@ -16284,7 +16348,11 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
@@ -16312,7 +16380,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -16392,11 +16460,7 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -16422,11 +16486,7 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
@@ -16512,7 +16572,11 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
@@ -16538,11 +16602,7 @@
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -16622,7 +16682,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -16650,7 +16710,11 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -16706,7 +16770,11 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
@@ -16732,7 +16800,11 @@
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
@@ -16758,7 +16830,11 @@
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
@@ -16914,11 +16990,7 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
@@ -16946,7 +17018,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -16974,7 +17046,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -17000,11 +17076,7 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
@@ -17060,11 +17132,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -17092,7 +17160,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -17120,11 +17188,7 @@
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
@@ -17150,7 +17214,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
@@ -17176,11 +17244,7 @@
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
@@ -17236,11 +17300,7 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
@@ -17266,7 +17326,11 @@
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
@@ -17294,7 +17358,7 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -17352,7 +17416,11 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
@@ -17434,7 +17502,11 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -17512,11 +17584,7 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
@@ -17542,11 +17610,7 @@
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
@@ -17572,11 +17636,7 @@
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
@@ -17658,11 +17718,7 @@
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
@@ -17688,11 +17744,7 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
@@ -17718,11 +17770,7 @@
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
@@ -17748,7 +17796,11 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
@@ -17774,7 +17826,11 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
@@ -17826,11 +17882,7 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -17856,11 +17908,7 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
@@ -17886,11 +17934,7 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
@@ -17948,7 +17992,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -17976,7 +18020,11 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
@@ -18002,11 +18050,7 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
@@ -18032,7 +18076,11 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
@@ -18140,11 +18188,7 @@
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
@@ -18170,11 +18214,7 @@
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
@@ -18200,7 +18240,11 @@
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
@@ -18256,7 +18300,11 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
@@ -18412,7 +18460,11 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
@@ -18438,7 +18490,11 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -18464,7 +18520,11 @@
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -18490,11 +18550,7 @@
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -18520,7 +18576,11 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
@@ -18546,7 +18606,11 @@
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
@@ -18598,7 +18662,11 @@
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
@@ -18624,7 +18692,11 @@
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -18650,11 +18722,7 @@
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
@@ -18682,7 +18750,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bearish Confluence</t>
+          <t>Bullish Confluence</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -18770,11 +18838,7 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
@@ -18826,7 +18890,11 @@
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
@@ -18880,7 +18948,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -18934,11 +19002,7 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -18990,11 +19054,7 @@
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -19020,11 +19080,7 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -19080,7 +19136,11 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
@@ -19106,7 +19166,11 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
@@ -19162,7 +19226,11 @@
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -19188,11 +19256,7 @@
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
@@ -19244,7 +19308,11 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
@@ -19430,14 +19498,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -19447,11 +19511,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABRITANNIA</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19532,14 +19592,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -19549,11 +19605,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19754,7 +19806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19822,7 +19874,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19845,7 +19897,37 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APATANJALI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>High Vol Expansion</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
         </is>
       </c>
     </row>
@@ -19954,7 +20036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20022,12 +20104,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -20041,19 +20123,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -20067,19 +20149,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCAMC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -20093,19 +20175,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHCLTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -20119,19 +20201,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -20145,14 +20227,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADALBHARAT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20171,19 +20253,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -20197,19 +20279,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJUBLFOOD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -20223,14 +20305,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDZINC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIXON</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CNXFINANCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20249,14 +20331,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXFINANCE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20275,19 +20357,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -20301,14 +20383,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CNXFINANCE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20327,19 +20409,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACAMS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -20353,19 +20435,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADLF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -20379,19 +20461,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORCEMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APRESTIGE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAM_INDIA</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -20405,19 +20487,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAM_INDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKNIFTY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -20431,19 +20513,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASTRAL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -20457,14 +20539,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20483,19 +20565,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -20509,7 +20591,241 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AONGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASONACOMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBILIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARVNL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANKIND</t>
         </is>
       </c>
     </row>
@@ -31986,7 +32302,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -32016,7 +32332,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -32046,7 +32362,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -32076,7 +32392,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -32136,7 +32452,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -32166,7 +32482,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -32196,7 +32512,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -32226,7 +32542,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -32256,7 +32572,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -32286,7 +32602,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -32316,7 +32632,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -32346,7 +32662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -32376,7 +32692,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -32436,7 +32752,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -32466,7 +32782,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -32496,7 +32812,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -32556,7 +32872,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -32616,7 +32932,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -32676,7 +32992,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -32706,7 +33022,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -32736,7 +33052,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -32766,7 +33082,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -32826,7 +33142,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -32856,7 +33172,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -32886,7 +33202,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -32946,7 +33262,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -33066,7 +33382,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -33096,7 +33412,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -33126,7 +33442,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -33156,7 +33472,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -33186,7 +33502,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -33216,7 +33532,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -33246,7 +33562,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -33276,7 +33592,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -33336,7 +33652,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -33366,7 +33682,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -33426,7 +33742,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -33456,7 +33772,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -33516,7 +33832,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -33546,7 +33862,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -33576,7 +33892,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -33606,7 +33922,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Weak Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -33636,7 +33952,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -33696,7 +34012,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -33726,7 +34042,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -33786,7 +34102,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -33816,7 +34132,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -33846,7 +34162,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -33876,7 +34192,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -33936,7 +34252,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -33966,7 +34282,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -33996,7 +34312,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -34026,7 +34342,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -34056,7 +34372,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -34086,7 +34402,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -34146,7 +34462,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -34176,7 +34492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -34236,7 +34552,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -34266,7 +34582,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -34326,7 +34642,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -34386,7 +34702,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -34416,7 +34732,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -34446,7 +34762,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -34476,7 +34792,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -34506,7 +34822,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -34566,7 +34882,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -34626,7 +34942,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -34686,7 +35002,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -34716,7 +35032,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -34746,7 +35062,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -34776,7 +35092,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -34806,7 +35122,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -34836,7 +35152,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -34866,7 +35182,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -34896,7 +35212,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -34926,7 +35242,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -34986,7 +35302,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -35016,7 +35332,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -35046,7 +35362,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -35076,7 +35392,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -35136,7 +35452,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -35256,7 +35572,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -35286,7 +35602,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -35316,7 +35632,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -35376,7 +35692,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -35406,7 +35722,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -35466,7 +35782,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -35496,7 +35812,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -35526,7 +35842,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -35556,7 +35872,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -35586,7 +35902,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -35616,7 +35932,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -35646,7 +35962,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -35766,7 +36082,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -35796,7 +36112,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -35886,7 +36202,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -35916,7 +36232,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -35946,7 +36262,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -35976,7 +36292,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -36006,7 +36322,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -36036,7 +36352,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -36096,7 +36412,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -36126,7 +36442,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -36156,7 +36472,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -36186,7 +36502,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -36216,7 +36532,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -36276,7 +36592,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -36306,7 +36622,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -36336,7 +36652,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -36396,7 +36712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -36456,7 +36772,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -36486,7 +36802,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -36516,7 +36832,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -36576,7 +36892,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -36606,7 +36922,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -36636,7 +36952,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -36666,7 +36982,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -36726,7 +37042,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -36756,7 +37072,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -36786,7 +37102,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -36846,7 +37162,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -36876,7 +37192,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -36906,7 +37222,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -36936,7 +37252,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -36966,7 +37282,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -36996,7 +37312,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -37026,7 +37342,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -37056,7 +37372,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -37086,7 +37402,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -37206,7 +37522,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -37236,7 +37552,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -37266,7 +37582,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -37296,7 +37612,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -37356,7 +37672,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -37386,7 +37702,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -37446,7 +37762,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -37476,7 +37792,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -37506,7 +37822,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -37536,7 +37852,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -37566,7 +37882,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -37596,7 +37912,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -37626,7 +37942,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -37656,7 +37972,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -37686,7 +38002,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -37776,7 +38092,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -37806,7 +38122,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -37836,7 +38152,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -37926,7 +38242,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -37986,7 +38302,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -38016,7 +38332,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -38046,7 +38362,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -38106,7 +38422,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -38136,7 +38452,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -38166,7 +38482,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -38196,7 +38512,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -38226,7 +38542,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -38256,7 +38572,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -38286,7 +38602,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -38316,7 +38632,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -38346,7 +38662,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -38376,7 +38692,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -38436,7 +38752,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -38777,11 +39093,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -38885,11 +39197,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -39019,7 +39327,11 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -39149,11 +39461,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -39257,11 +39565,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -39287,11 +39591,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -39317,11 +39617,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -39481,11 +39777,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -39537,11 +39829,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -39567,11 +39855,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -39623,7 +39907,11 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -39701,7 +39989,11 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -39831,7 +40123,11 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -39857,11 +40153,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -39913,11 +40205,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -40021,11 +40309,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -40103,7 +40387,11 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -40341,11 +40629,7 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -40449,11 +40733,7 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -40505,11 +40785,7 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -40613,7 +40889,11 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -40773,11 +41053,7 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -40855,11 +41131,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -40911,7 +41183,11 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -40989,11 +41265,7 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -41201,11 +41473,7 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
@@ -41413,11 +41681,7 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -41443,7 +41707,11 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -41469,7 +41737,11 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
@@ -41625,7 +41897,11 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -41651,7 +41927,11 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -41759,11 +42039,7 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -41841,7 +42117,11 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -41919,7 +42199,11 @@
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -42187,11 +42471,7 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -42559,11 +42839,7 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -42779,7 +43055,11 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -43017,7 +43297,11 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -43255,7 +43539,11 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
@@ -43437,11 +43725,7 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -43649,11 +43933,7 @@
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
@@ -43757,11 +44037,7 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
@@ -43787,11 +44063,7 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
@@ -43925,11 +44197,7 @@
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
@@ -43981,11 +44249,7 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
@@ -44011,11 +44275,7 @@
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
@@ -44093,11 +44353,7 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
@@ -44123,11 +44379,7 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
@@ -44205,7 +44457,11 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
@@ -44532,7 +44788,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -44756,11 +45016,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -44786,11 +45042,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -44816,7 +45068,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -44994,7 +45250,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Strong Downtrend</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -45142,11 +45398,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -45292,7 +45544,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -45408,11 +45664,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -45498,11 +45750,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -45528,11 +45776,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -45588,7 +45832,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -45782,11 +46030,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -45874,7 +46118,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Strong Downtrend</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -45992,11 +46236,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -46048,11 +46288,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -46108,7 +46344,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -46310,11 +46550,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -46752,11 +46988,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -46838,11 +47070,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -46988,7 +47216,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -47014,7 +47246,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -47162,7 +47398,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Strong Downtrend</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -47220,11 +47456,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -47366,11 +47598,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -47396,7 +47624,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
@@ -47628,11 +47860,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -47950,11 +48178,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
@@ -48036,11 +48260,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -48066,11 +48286,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
@@ -48246,11 +48462,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -48302,11 +48514,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
@@ -48422,7 +48630,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
@@ -48448,11 +48660,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
@@ -48654,11 +48862,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
@@ -48800,11 +49004,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
@@ -49118,11 +49318,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -49230,7 +49426,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -49316,11 +49516,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -49346,11 +49542,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -49406,11 +49598,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
@@ -49436,7 +49624,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
@@ -49790,7 +49982,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Strong Downtrend</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -49876,7 +50068,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Strong Downtrend</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -49964,7 +50156,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
@@ -50020,11 +50216,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
@@ -50052,7 +50244,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Strong Downtrend</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -50110,11 +50302,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -50318,7 +50506,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Strong Downtrend</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -50376,7 +50564,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
